--- a/results/qwen3_8b/comparison_ToTRAG/ToTRAG_costs.xlsx
+++ b/results/qwen3_8b/comparison_ToTRAG/ToTRAG_costs.xlsx
@@ -472,13 +472,13 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>211.3978805541992</v>
+        <v>310.8729336261749</v>
       </c>
       <c r="B2" t="n">
-        <v>1423.0078125</v>
+        <v>1440.953125</v>
       </c>
       <c r="C2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D2" t="n">
         <v>20</v>
@@ -487,10 +487,10 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9461557865142822</v>
+        <v>1.202955007553101</v>
       </c>
       <c r="G2" t="n">
-        <v>210.4517211914062</v>
+        <v>309.6699740886688</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -498,13 +498,13 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>178.1337730884552</v>
+        <v>167.1431570053101</v>
       </c>
       <c r="B3" t="n">
-        <v>1423.21484375</v>
+        <v>1441.18359375</v>
       </c>
       <c r="C3" t="n">
-        <v>13.2</v>
+        <v>13.7</v>
       </c>
       <c r="D3" t="n">
         <v>20</v>
@@ -513,10 +513,10 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>1.448410034179688</v>
+        <v>1.503925800323486</v>
       </c>
       <c r="G3" t="n">
-        <v>176.6853597164154</v>
+        <v>165.639228105545</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -524,13 +524,13 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>148.4784555435181</v>
+        <v>202.0801162719727</v>
       </c>
       <c r="B4" t="n">
-        <v>1423.21875</v>
+        <v>1441.3828125</v>
       </c>
       <c r="C4" t="n">
-        <v>13.2</v>
+        <v>13.5</v>
       </c>
       <c r="D4" t="n">
         <v>20</v>
@@ -539,10 +539,10 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>1.32028603553772</v>
+        <v>1.309788465499878</v>
       </c>
       <c r="G4" t="n">
-        <v>147.1581671237946</v>
+        <v>200.770325422287</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -550,13 +550,13 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>183.1602656841278</v>
+        <v>189.0723538398743</v>
       </c>
       <c r="B5" t="n">
-        <v>1423.37109375</v>
+        <v>1442.5859375</v>
       </c>
       <c r="C5" t="n">
-        <v>13.3</v>
+        <v>13.5</v>
       </c>
       <c r="D5" t="n">
         <v>20</v>
@@ -565,10 +565,10 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>1.461454153060913</v>
+        <v>1.206163644790649</v>
       </c>
       <c r="G5" t="n">
-        <v>181.698807477951</v>
+        <v>187.866188287735</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -576,13 +576,13 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>143.5443737506866</v>
+        <v>161.7180795669556</v>
       </c>
       <c r="B6" t="n">
-        <v>1423.515625</v>
+        <v>1442.84765625</v>
       </c>
       <c r="C6" t="n">
-        <v>13.3</v>
+        <v>13.7</v>
       </c>
       <c r="D6" t="n">
         <v>20</v>
@@ -591,10 +591,10 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>1.243539571762085</v>
+        <v>1.223984956741333</v>
       </c>
       <c r="G6" t="n">
-        <v>142.3008322715759</v>
+        <v>160.4940919876099</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -602,13 +602,13 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>331.4431223869324</v>
+        <v>305.1571083068848</v>
       </c>
       <c r="B7" t="n">
-        <v>1424.984375</v>
+        <v>1443.47265625</v>
       </c>
       <c r="C7" t="n">
-        <v>13.4</v>
+        <v>13.9</v>
       </c>
       <c r="D7" t="n">
         <v>20</v>
@@ -617,10 +617,10 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>1.218279600143433</v>
+        <v>1.205789089202881</v>
       </c>
       <c r="G7" t="n">
-        <v>330.2248401641846</v>
+        <v>303.9513173103333</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -628,13 +628,13 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>285.5549674034119</v>
+        <v>177.4175817966461</v>
       </c>
       <c r="B8" t="n">
-        <v>1424.984375</v>
+        <v>1443.6015625</v>
       </c>
       <c r="C8" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="D8" t="n">
         <v>20</v>
@@ -643,10 +643,10 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>1.554473638534546</v>
+        <v>1.230495691299438</v>
       </c>
       <c r="G8" t="n">
-        <v>284.0004913806915</v>
+        <v>176.1870834827423</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -654,13 +654,13 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>209.1037220954895</v>
+        <v>201.1769127845764</v>
       </c>
       <c r="B9" t="n">
-        <v>1424.984375</v>
+        <v>1443.60546875</v>
       </c>
       <c r="C9" t="n">
-        <v>13.3</v>
+        <v>13.5</v>
       </c>
       <c r="D9" t="n">
         <v>20</v>
@@ -669,10 +669,10 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>1.291558504104614</v>
+        <v>1.249756097793579</v>
       </c>
       <c r="G9" t="n">
-        <v>207.8121614456177</v>
+        <v>199.9271540641785</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -680,13 +680,13 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>196.254499912262</v>
+        <v>195.3745613098145</v>
       </c>
       <c r="B10" t="n">
-        <v>1424.984375</v>
+        <v>1443.6875</v>
       </c>
       <c r="C10" t="n">
-        <v>13.3</v>
+        <v>13.7</v>
       </c>
       <c r="D10" t="n">
         <v>20</v>
@@ -695,10 +695,10 @@
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>1.228546142578125</v>
+        <v>1.255224704742432</v>
       </c>
       <c r="G10" t="n">
-        <v>195.0259521007538</v>
+        <v>194.1193339824677</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -706,13 +706,13 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>202.4620254039764</v>
+        <v>207.230345249176</v>
       </c>
       <c r="B11" t="n">
-        <v>1424.984375</v>
+        <v>1443.6953125</v>
       </c>
       <c r="C11" t="n">
-        <v>13.1</v>
+        <v>13.7</v>
       </c>
       <c r="D11" t="n">
         <v>20</v>
@@ -721,10 +721,10 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>1.489540576934814</v>
+        <v>1.271144151687622</v>
       </c>
       <c r="G11" t="n">
-        <v>200.972482919693</v>
+        <v>205.9591982364655</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -732,13 +732,13 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>204.6425461769104</v>
+        <v>235.5697114467621</v>
       </c>
       <c r="B12" t="n">
-        <v>1424.984375</v>
+        <v>1443.7578125</v>
       </c>
       <c r="C12" t="n">
-        <v>13.4</v>
+        <v>13.8</v>
       </c>
       <c r="D12" t="n">
         <v>20</v>
@@ -747,10 +747,10 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>1.255172967910767</v>
+        <v>1.214060306549072</v>
       </c>
       <c r="G12" t="n">
-        <v>203.3873710632324</v>
+        <v>234.3556480407715</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -758,13 +758,13 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>183.3079771995544</v>
+        <v>199.3811047077179</v>
       </c>
       <c r="B13" t="n">
-        <v>1424.984375</v>
+        <v>1443.7578125</v>
       </c>
       <c r="C13" t="n">
-        <v>13.3</v>
+        <v>13.7</v>
       </c>
       <c r="D13" t="n">
         <v>20</v>
@@ -773,10 +773,10 @@
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>1.484333276748657</v>
+        <v>1.250001907348633</v>
       </c>
       <c r="G13" t="n">
-        <v>181.8236410617828</v>
+        <v>198.1311006546021</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -784,13 +784,13 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>238.224672794342</v>
+        <v>165.5595126152039</v>
       </c>
       <c r="B14" t="n">
-        <v>1424.984375</v>
+        <v>1443.7578125</v>
       </c>
       <c r="C14" t="n">
-        <v>13</v>
+        <v>13.3</v>
       </c>
       <c r="D14" t="n">
         <v>20</v>
@@ -799,10 +799,10 @@
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>1.296699523925781</v>
+        <v>1.259896755218506</v>
       </c>
       <c r="G14" t="n">
-        <v>236.9279713630676</v>
+        <v>164.2996129989624</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -810,13 +810,13 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>202.8805346488953</v>
+        <v>146.7446558475494</v>
       </c>
       <c r="B15" t="n">
-        <v>1424.984375</v>
+        <v>1443.76171875</v>
       </c>
       <c r="C15" t="n">
-        <v>13.4</v>
+        <v>13.7</v>
       </c>
       <c r="D15" t="n">
         <v>20</v>
@@ -825,10 +825,10 @@
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>1.465949296951294</v>
+        <v>1.292887210845947</v>
       </c>
       <c r="G15" t="n">
-        <v>201.4145829677582</v>
+        <v>145.4517657756805</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -836,13 +836,13 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>184.6559479236603</v>
+        <v>155.9911365509033</v>
       </c>
       <c r="B16" t="n">
-        <v>1424.984375</v>
+        <v>1443.765625</v>
       </c>
       <c r="C16" t="n">
-        <v>13.3</v>
+        <v>13.6</v>
       </c>
       <c r="D16" t="n">
         <v>20</v>
@@ -851,10 +851,10 @@
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>1.216969966888428</v>
+        <v>1.258129835128784</v>
       </c>
       <c r="G16" t="n">
-        <v>183.4389758110046</v>
+        <v>154.7330040931702</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -862,10 +862,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>225.6616806983948</v>
+        <v>176.6943078041077</v>
       </c>
       <c r="B17" t="n">
-        <v>1424.98828125</v>
+        <v>1443.82421875</v>
       </c>
       <c r="C17" t="n">
         <v>13.5</v>
@@ -877,10 +877,10 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>1.252410888671875</v>
+        <v>1.258592844009399</v>
       </c>
       <c r="G17" t="n">
-        <v>224.4092671871185</v>
+        <v>175.4357128143311</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -888,13 +888,13 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>181.3436617851257</v>
+        <v>236.8438758850098</v>
       </c>
       <c r="B18" t="n">
-        <v>1424.98828125</v>
+        <v>1443.828125</v>
       </c>
       <c r="C18" t="n">
-        <v>13.4</v>
+        <v>13.9</v>
       </c>
       <c r="D18" t="n">
         <v>20</v>
@@ -903,10 +903,10 @@
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>1.27207088470459</v>
+        <v>1.245406150817871</v>
       </c>
       <c r="G18" t="n">
-        <v>180.0715887546539</v>
+        <v>235.5984673500061</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -914,13 +914,13 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>252.1928403377533</v>
+        <v>182.3371558189392</v>
       </c>
       <c r="B19" t="n">
-        <v>1424.98828125</v>
+        <v>1443.83203125</v>
       </c>
       <c r="C19" t="n">
-        <v>13.4</v>
+        <v>13.6</v>
       </c>
       <c r="D19" t="n">
         <v>20</v>
@@ -929,10 +929,10 @@
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>1.243606805801392</v>
+        <v>1.275394916534424</v>
       </c>
       <c r="G19" t="n">
-        <v>250.949230670929</v>
+        <v>181.061758518219</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -940,13 +940,13 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>195.9814608097076</v>
+        <v>187.0562489032745</v>
       </c>
       <c r="B20" t="n">
-        <v>1424.98828125</v>
+        <v>1443.83203125</v>
       </c>
       <c r="C20" t="n">
-        <v>13.5</v>
+        <v>13.4</v>
       </c>
       <c r="D20" t="n">
         <v>20</v>
@@ -955,10 +955,10 @@
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>1.453266859054565</v>
+        <v>1.238818168640137</v>
       </c>
       <c r="G20" t="n">
-        <v>194.5281913280487</v>
+        <v>185.8174278736115</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -966,13 +966,13 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>184.6234850883484</v>
+        <v>275.7304401397705</v>
       </c>
       <c r="B21" t="n">
-        <v>1424.98828125</v>
+        <v>1444.95703125</v>
       </c>
       <c r="C21" t="n">
-        <v>13.2</v>
+        <v>13.5</v>
       </c>
       <c r="D21" t="n">
         <v>20</v>
@@ -981,10 +981,10 @@
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>1.478805065155029</v>
+        <v>1.421154975891113</v>
       </c>
       <c r="G21" t="n">
-        <v>183.144677400589</v>
+        <v>274.3092832565308</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
@@ -992,13 +992,13 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>171.9529812335968</v>
+        <v>196.696005821228</v>
       </c>
       <c r="B22" t="n">
-        <v>1424.98828125</v>
+        <v>1444.95703125</v>
       </c>
       <c r="C22" t="n">
-        <v>13.3</v>
+        <v>13.7</v>
       </c>
       <c r="D22" t="n">
         <v>20</v>
@@ -1007,10 +1007,10 @@
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>1.472054004669189</v>
+        <v>1.471139430999756</v>
       </c>
       <c r="G22" t="n">
-        <v>170.4809243679047</v>
+        <v>195.2248642444611</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
@@ -1018,13 +1018,13 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>248.1762750148773</v>
+        <v>186.1756653785706</v>
       </c>
       <c r="B23" t="n">
-        <v>1424.98828125</v>
+        <v>1444.95703125</v>
       </c>
       <c r="C23" t="n">
-        <v>13.3</v>
+        <v>13.6</v>
       </c>
       <c r="D23" t="n">
         <v>20</v>
@@ -1033,10 +1033,10 @@
         <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>1.248279809951782</v>
+        <v>1.253982782363892</v>
       </c>
       <c r="G23" t="n">
-        <v>246.9279928207397</v>
+        <v>184.9216799736023</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -1044,13 +1044,13 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>153.3569903373718</v>
+        <v>139.8938827514648</v>
       </c>
       <c r="B24" t="n">
-        <v>1424.98828125</v>
+        <v>1444.95703125</v>
       </c>
       <c r="C24" t="n">
-        <v>13.3</v>
+        <v>13.5</v>
       </c>
       <c r="D24" t="n">
         <v>20</v>
@@ -1059,10 +1059,10 @@
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>1.231390714645386</v>
+        <v>1.265970945358276</v>
       </c>
       <c r="G24" t="n">
-        <v>152.1255972385406</v>
+        <v>138.627908706665</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -1070,13 +1070,13 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>195.9576551914215</v>
+        <v>201.1525661945343</v>
       </c>
       <c r="B25" t="n">
-        <v>1424.98828125</v>
+        <v>1444.95703125</v>
       </c>
       <c r="C25" t="n">
-        <v>13.3</v>
+        <v>13.8</v>
       </c>
       <c r="D25" t="n">
         <v>20</v>
@@ -1085,10 +1085,10 @@
         <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>1.414610385894775</v>
+        <v>1.27272629737854</v>
       </c>
       <c r="G25" t="n">
-        <v>194.5430421829224</v>
+        <v>199.8798377513885</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
@@ -1096,13 +1096,13 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>162.7423067092896</v>
+        <v>161.6218037605286</v>
       </c>
       <c r="B26" t="n">
-        <v>1424.98828125</v>
+        <v>1444.95703125</v>
       </c>
       <c r="C26" t="n">
-        <v>13.3</v>
+        <v>13.6</v>
       </c>
       <c r="D26" t="n">
         <v>20</v>
@@ -1111,10 +1111,10 @@
         <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>1.257335662841797</v>
+        <v>1.283930540084839</v>
       </c>
       <c r="G26" t="n">
-        <v>161.484968662262</v>
+        <v>160.3378708362579</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -1122,13 +1122,13 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>178.2678775787354</v>
+        <v>128.6752142906189</v>
       </c>
       <c r="B27" t="n">
-        <v>1424.98828125</v>
+        <v>1444.95703125</v>
       </c>
       <c r="C27" t="n">
-        <v>13.2</v>
+        <v>13.5</v>
       </c>
       <c r="D27" t="n">
         <v>20</v>
@@ -1137,10 +1137,10 @@
         <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>1.450373649597168</v>
+        <v>1.421056509017944</v>
       </c>
       <c r="G27" t="n">
-        <v>176.817501783371</v>
+        <v>127.254154920578</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
@@ -1148,13 +1148,13 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>192.0386333465576</v>
+        <v>164.7901599407196</v>
       </c>
       <c r="B28" t="n">
-        <v>1424.9921875</v>
+        <v>1444.95703125</v>
       </c>
       <c r="C28" t="n">
-        <v>13.4</v>
+        <v>13.7</v>
       </c>
       <c r="D28" t="n">
         <v>20</v>
@@ -1163,10 +1163,10 @@
         <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>1.255966186523438</v>
+        <v>1.232701539993286</v>
       </c>
       <c r="G28" t="n">
-        <v>190.782665014267</v>
+        <v>163.5574557781219</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
@@ -1174,10 +1174,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>165.5448276996613</v>
+        <v>161.3088953495026</v>
       </c>
       <c r="B29" t="n">
-        <v>1424.9921875</v>
+        <v>1444.95703125</v>
       </c>
       <c r="C29" t="n">
         <v>13.4</v>
@@ -1189,10 +1189,10 @@
         <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>1.487584352493286</v>
+        <v>1.199329614639282</v>
       </c>
       <c r="G29" t="n">
-        <v>164.0572414398193</v>
+        <v>160.1095628738403</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
@@ -1200,13 +1200,13 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>152.6218583583832</v>
+        <v>158.4059700965881</v>
       </c>
       <c r="B30" t="n">
-        <v>1424.9921875</v>
+        <v>1444.95703125</v>
       </c>
       <c r="C30" t="n">
-        <v>13.2</v>
+        <v>13.5</v>
       </c>
       <c r="D30" t="n">
         <v>20</v>
@@ -1215,10 +1215,10 @@
         <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>1.466865301132202</v>
+        <v>1.224895238876343</v>
       </c>
       <c r="G30" t="n">
-        <v>151.1549906730652</v>
+        <v>157.1810719966888</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
@@ -1226,13 +1226,13 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>137.4919800758362</v>
+        <v>193.4756245613098</v>
       </c>
       <c r="B31" t="n">
-        <v>1424.99609375</v>
+        <v>1444.95703125</v>
       </c>
       <c r="C31" t="n">
-        <v>13</v>
+        <v>13.8</v>
       </c>
       <c r="D31" t="n">
         <v>20</v>
@@ -1241,10 +1241,10 @@
         <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>1.25250244140625</v>
+        <v>1.295840978622437</v>
       </c>
       <c r="G31" t="n">
-        <v>136.239474773407</v>
+        <v>192.179780960083</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
@@ -1252,13 +1252,13 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>177.6062071323395</v>
+        <v>121.3822572231293</v>
       </c>
       <c r="B32" t="n">
-        <v>1424.99609375</v>
+        <v>1444.95703125</v>
       </c>
       <c r="C32" t="n">
-        <v>13.3</v>
+        <v>13.5</v>
       </c>
       <c r="D32" t="n">
         <v>20</v>
@@ -1267,10 +1267,10 @@
         <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>1.489733934402466</v>
+        <v>1.264864206314087</v>
       </c>
       <c r="G32" t="n">
-        <v>176.1164700984955</v>
+        <v>120.1173901557922</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -1278,13 +1278,13 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>164.8091218471527</v>
+        <v>195.1440138816833</v>
       </c>
       <c r="B33" t="n">
-        <v>1424.99609375</v>
+        <v>1444.95703125</v>
       </c>
       <c r="C33" t="n">
-        <v>13.4</v>
+        <v>13.8</v>
       </c>
       <c r="D33" t="n">
         <v>20</v>
@@ -1293,10 +1293,10 @@
         <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>1.475674867630005</v>
+        <v>1.455668449401855</v>
       </c>
       <c r="G33" t="n">
-        <v>163.3334443569183</v>
+        <v>193.6883425712585</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
@@ -1304,13 +1304,13 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>186.9021782875061</v>
+        <v>217.3669555187225</v>
       </c>
       <c r="B34" t="n">
-        <v>1425</v>
+        <v>1444.95703125</v>
       </c>
       <c r="C34" t="n">
-        <v>13.2</v>
+        <v>13.7</v>
       </c>
       <c r="D34" t="n">
         <v>20</v>
@@ -1319,10 +1319,10 @@
         <v>0</v>
       </c>
       <c r="F34" t="n">
-        <v>1.50193190574646</v>
+        <v>1.510351181030273</v>
       </c>
       <c r="G34" t="n">
-        <v>185.4002432823181</v>
+        <v>215.856602191925</v>
       </c>
       <c r="H34" t="n">
         <v>0</v>
@@ -1330,13 +1330,13 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>184.8952910900116</v>
+        <v>227.4000310897827</v>
       </c>
       <c r="B35" t="n">
-        <v>1425</v>
+        <v>1444.95703125</v>
       </c>
       <c r="C35" t="n">
-        <v>13.3</v>
+        <v>13.7</v>
       </c>
       <c r="D35" t="n">
         <v>20</v>
@@ -1345,10 +1345,10 @@
         <v>0</v>
       </c>
       <c r="F35" t="n">
-        <v>1.482797145843506</v>
+        <v>1.460640430450439</v>
       </c>
       <c r="G35" t="n">
-        <v>183.4124920368195</v>
+        <v>225.9393885135651</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
@@ -1356,13 +1356,13 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>187.1887955665588</v>
+        <v>198.508585691452</v>
       </c>
       <c r="B36" t="n">
-        <v>1425.00390625</v>
+        <v>1444.95703125</v>
       </c>
       <c r="C36" t="n">
-        <v>13.3</v>
+        <v>13.9</v>
       </c>
       <c r="D36" t="n">
         <v>20</v>
@@ -1371,10 +1371,10 @@
         <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>1.483514785766602</v>
+        <v>1.43293571472168</v>
       </c>
       <c r="G36" t="n">
-        <v>185.7052788734436</v>
+        <v>197.075647354126</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
@@ -1382,13 +1382,13 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>238.1522080898285</v>
+        <v>159.1446752548218</v>
       </c>
       <c r="B37" t="n">
-        <v>1425.00390625</v>
+        <v>1444.95703125</v>
       </c>
       <c r="C37" t="n">
-        <v>13.4</v>
+        <v>13.7</v>
       </c>
       <c r="D37" t="n">
         <v>20</v>
@@ -1397,10 +1397,10 @@
         <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>1.718215465545654</v>
+        <v>1.436980962753296</v>
       </c>
       <c r="G37" t="n">
-        <v>236.433990240097</v>
+        <v>157.7076916694641</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
@@ -1408,13 +1408,13 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>196.4047248363495</v>
+        <v>173.7477879524231</v>
       </c>
       <c r="B38" t="n">
-        <v>1425.0078125</v>
+        <v>1444.95703125</v>
       </c>
       <c r="C38" t="n">
-        <v>13.3</v>
+        <v>13.6</v>
       </c>
       <c r="D38" t="n">
         <v>20</v>
@@ -1423,10 +1423,10 @@
         <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>1.5500807762146</v>
+        <v>1.440690279006958</v>
       </c>
       <c r="G38" t="n">
-        <v>194.8546423912048</v>
+        <v>172.3070952892303</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -1434,13 +1434,13 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>175.4318835735321</v>
+        <v>179.0830910205841</v>
       </c>
       <c r="B39" t="n">
-        <v>1425.01171875</v>
+        <v>1444.95703125</v>
       </c>
       <c r="C39" t="n">
-        <v>13.2</v>
+        <v>13.8</v>
       </c>
       <c r="D39" t="n">
         <v>20</v>
@@ -1449,10 +1449,10 @@
         <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>1.479482650756836</v>
+        <v>1.216558218002319</v>
       </c>
       <c r="G39" t="n">
-        <v>173.9523987770081</v>
+        <v>177.8665306568146</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
@@ -1460,13 +1460,13 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>184.301105260849</v>
+        <v>175.5190346240997</v>
       </c>
       <c r="B40" t="n">
-        <v>1425.01171875</v>
+        <v>1444.95703125</v>
       </c>
       <c r="C40" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="D40" t="n">
         <v>20</v>
@@ -1475,10 +1475,10 @@
         <v>0</v>
       </c>
       <c r="F40" t="n">
-        <v>1.265569925308228</v>
+        <v>1.229546070098877</v>
       </c>
       <c r="G40" t="n">
-        <v>183.0355336666107</v>
+        <v>174.2894859313965</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
@@ -1486,10 +1486,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>233.9566657543182</v>
+        <v>142.5459773540497</v>
       </c>
       <c r="B41" t="n">
-        <v>1425.01171875</v>
+        <v>1444.95703125</v>
       </c>
       <c r="C41" t="n">
         <v>13.4</v>
@@ -1501,10 +1501,10 @@
         <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>1.321363925933838</v>
+        <v>1.24233078956604</v>
       </c>
       <c r="G41" t="n">
-        <v>232.63529920578</v>
+        <v>141.3036441802979</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
@@ -1512,13 +1512,13 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>145.607213973999</v>
+        <v>183.410521030426</v>
       </c>
       <c r="B42" t="n">
-        <v>1425.01171875</v>
+        <v>1444.95703125</v>
       </c>
       <c r="C42" t="n">
-        <v>13.3</v>
+        <v>13.7</v>
       </c>
       <c r="D42" t="n">
         <v>20</v>
@@ -1527,10 +1527,10 @@
         <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>1.283554077148438</v>
+        <v>1.250130891799927</v>
       </c>
       <c r="G42" t="n">
-        <v>144.323657989502</v>
+        <v>182.1603875160217</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
@@ -1538,13 +1538,13 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>178.2386455535889</v>
+        <v>183.941831111908</v>
       </c>
       <c r="B43" t="n">
-        <v>1425.01953125</v>
+        <v>1444.95703125</v>
       </c>
       <c r="C43" t="n">
-        <v>13.2</v>
+        <v>13.8</v>
       </c>
       <c r="D43" t="n">
         <v>20</v>
@@ -1553,10 +1553,10 @@
         <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>1.479412078857422</v>
+        <v>1.238771200180054</v>
       </c>
       <c r="G43" t="n">
-        <v>176.7592308521271</v>
+        <v>182.7030580043793</v>
       </c>
       <c r="H43" t="n">
         <v>0</v>
@@ -1564,13 +1564,13 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>179.8782074451447</v>
+        <v>187.4687716960907</v>
       </c>
       <c r="B44" t="n">
-        <v>1425.01953125</v>
+        <v>1444.95703125</v>
       </c>
       <c r="C44" t="n">
-        <v>13.2</v>
+        <v>13.6</v>
       </c>
       <c r="D44" t="n">
         <v>20</v>
@@ -1579,10 +1579,10 @@
         <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>1.256341695785522</v>
+        <v>1.239312648773193</v>
       </c>
       <c r="G44" t="n">
-        <v>178.6218569278717</v>
+        <v>186.2294566631317</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
@@ -1590,13 +1590,13 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>196.1939218044281</v>
+        <v>201.6903517246246</v>
       </c>
       <c r="B45" t="n">
-        <v>1425.09765625</v>
+        <v>1445.1484375</v>
       </c>
       <c r="C45" t="n">
-        <v>13.4</v>
+        <v>13.8</v>
       </c>
       <c r="D45" t="n">
         <v>20</v>
@@ -1605,10 +1605,10 @@
         <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>1.50542950630188</v>
+        <v>1.424128293991089</v>
       </c>
       <c r="G45" t="n">
-        <v>194.688490152359</v>
+        <v>200.2662200927734</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
@@ -1616,13 +1616,13 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>249.3245465755463</v>
+        <v>207.9434475898743</v>
       </c>
       <c r="B46" t="n">
-        <v>1425.09765625</v>
+        <v>1445.1484375</v>
       </c>
       <c r="C46" t="n">
-        <v>13.5</v>
+        <v>13.7</v>
       </c>
       <c r="D46" t="n">
         <v>20</v>
@@ -1631,10 +1631,10 @@
         <v>0</v>
       </c>
       <c r="F46" t="n">
-        <v>1.473270893096924</v>
+        <v>1.241191625595093</v>
       </c>
       <c r="G46" t="n">
-        <v>247.8512737751007</v>
+        <v>206.7022526264191</v>
       </c>
       <c r="H46" t="n">
         <v>0</v>
@@ -1642,13 +1642,13 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>253.3274230957031</v>
+        <v>190.2458679676056</v>
       </c>
       <c r="B47" t="n">
-        <v>1425.33984375</v>
+        <v>1445.15234375</v>
       </c>
       <c r="C47" t="n">
-        <v>13.3</v>
+        <v>13.6</v>
       </c>
       <c r="D47" t="n">
         <v>20</v>
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="F47" t="n">
-        <v>1.722072839736938</v>
+        <v>1.499740123748779</v>
       </c>
       <c r="G47" t="n">
-        <v>251.6053471565247</v>
+        <v>188.7461249828339</v>
       </c>
       <c r="H47" t="n">
         <v>0</v>
@@ -1668,10 +1668,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>215.6842575073242</v>
+        <v>142.4149215221405</v>
       </c>
       <c r="B48" t="n">
-        <v>1425.33984375</v>
+        <v>1445.15625</v>
       </c>
       <c r="C48" t="n">
         <v>13.5</v>
@@ -1683,10 +1683,10 @@
         <v>0</v>
       </c>
       <c r="F48" t="n">
-        <v>1.462792158126831</v>
+        <v>1.243967294692993</v>
       </c>
       <c r="G48" t="n">
-        <v>214.221462726593</v>
+        <v>141.1709518432617</v>
       </c>
       <c r="H48" t="n">
         <v>0</v>
@@ -1694,13 +1694,13 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>165.2751212120056</v>
+        <v>210.7453303337097</v>
       </c>
       <c r="B49" t="n">
-        <v>1425.33984375</v>
+        <v>1445.15625</v>
       </c>
       <c r="C49" t="n">
-        <v>13.4</v>
+        <v>13.8</v>
       </c>
       <c r="D49" t="n">
         <v>20</v>
@@ -1709,10 +1709,10 @@
         <v>0</v>
       </c>
       <c r="F49" t="n">
-        <v>1.48877739906311</v>
+        <v>1.231613636016846</v>
       </c>
       <c r="G49" t="n">
-        <v>163.7863421440125</v>
+        <v>209.5137135982513</v>
       </c>
       <c r="H49" t="n">
         <v>0</v>
@@ -1720,13 +1720,13 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>172.670286655426</v>
+        <v>187.8110489845276</v>
       </c>
       <c r="B50" t="n">
-        <v>1425.33984375</v>
+        <v>1445.16015625</v>
       </c>
       <c r="C50" t="n">
-        <v>13.1</v>
+        <v>13.7</v>
       </c>
       <c r="D50" t="n">
         <v>20</v>
@@ -1735,10 +1735,10 @@
         <v>0</v>
       </c>
       <c r="F50" t="n">
-        <v>1.481330394744873</v>
+        <v>1.217814922332764</v>
       </c>
       <c r="G50" t="n">
-        <v>171.1889541149139</v>
+        <v>186.5932309627533</v>
       </c>
       <c r="H50" t="n">
         <v>0</v>
@@ -1746,13 +1746,13 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>315.2179067134857</v>
+        <v>263.0424222946167</v>
       </c>
       <c r="B51" t="n">
-        <v>1425.6796875</v>
+        <v>1445.1640625</v>
       </c>
       <c r="C51" t="n">
-        <v>13.5</v>
+        <v>13.8</v>
       </c>
       <c r="D51" t="n">
         <v>20</v>
@@ -1761,10 +1761,10 @@
         <v>0</v>
       </c>
       <c r="F51" t="n">
-        <v>1.511498689651489</v>
+        <v>1.434489727020264</v>
       </c>
       <c r="G51" t="n">
-        <v>313.7064056396484</v>
+        <v>261.6079299449921</v>
       </c>
       <c r="H51" t="n">
         <v>0</v>
@@ -1772,13 +1772,13 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>176.9254086017609</v>
+        <v>203.0529260635376</v>
       </c>
       <c r="B52" t="n">
-        <v>1425.6796875</v>
+        <v>1445.171875</v>
       </c>
       <c r="C52" t="n">
-        <v>13.2</v>
+        <v>13.8</v>
       </c>
       <c r="D52" t="n">
         <v>20</v>
@@ -1787,10 +1787,10 @@
         <v>0</v>
       </c>
       <c r="F52" t="n">
-        <v>1.504750967025757</v>
+        <v>1.292034864425659</v>
       </c>
       <c r="G52" t="n">
-        <v>175.4206552505493</v>
+        <v>201.7608885765076</v>
       </c>
       <c r="H52" t="n">
         <v>0</v>
@@ -1798,13 +1798,13 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>233.0190327167511</v>
+        <v>225.9946026802063</v>
       </c>
       <c r="B53" t="n">
-        <v>1425.6796875</v>
+        <v>1445.40234375</v>
       </c>
       <c r="C53" t="n">
-        <v>13.4</v>
+        <v>13.7</v>
       </c>
       <c r="D53" t="n">
         <v>20</v>
@@ -1813,10 +1813,10 @@
         <v>0</v>
       </c>
       <c r="F53" t="n">
-        <v>1.48765230178833</v>
+        <v>1.44616436958313</v>
       </c>
       <c r="G53" t="n">
-        <v>231.5313785076141</v>
+        <v>224.5484359264374</v>
       </c>
       <c r="H53" t="n">
         <v>0</v>
@@ -1824,13 +1824,13 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>203.4117324352264</v>
+        <v>264.5489459037781</v>
       </c>
       <c r="B54" t="n">
-        <v>1425.6796875</v>
+        <v>1445.41015625</v>
       </c>
       <c r="C54" t="n">
-        <v>13.4</v>
+        <v>13.9</v>
       </c>
       <c r="D54" t="n">
         <v>20</v>
@@ -1839,10 +1839,10 @@
         <v>0</v>
       </c>
       <c r="F54" t="n">
-        <v>1.287887334823608</v>
+        <v>1.1799476146698</v>
       </c>
       <c r="G54" t="n">
-        <v>202.123842716217</v>
+        <v>263.3689961433411</v>
       </c>
       <c r="H54" t="n">
         <v>0</v>
@@ -1850,13 +1850,13 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>198.3057036399841</v>
+        <v>206.7777540683746</v>
       </c>
       <c r="B55" t="n">
-        <v>1425.6796875</v>
+        <v>1445.4140625</v>
       </c>
       <c r="C55" t="n">
-        <v>13.4</v>
+        <v>13.7</v>
       </c>
       <c r="D55" t="n">
         <v>20</v>
@@ -1865,10 +1865,10 @@
         <v>0</v>
       </c>
       <c r="F55" t="n">
-        <v>1.253013610839844</v>
+        <v>1.216771125793457</v>
       </c>
       <c r="G55" t="n">
-        <v>197.0526881217957</v>
+        <v>205.5609812736511</v>
       </c>
       <c r="H55" t="n">
         <v>0</v>
@@ -1876,13 +1876,13 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>197.0316779613495</v>
+        <v>202.7357501983643</v>
       </c>
       <c r="B56" t="n">
-        <v>1425.6796875</v>
+        <v>1445.41796875</v>
       </c>
       <c r="C56" t="n">
-        <v>13.4</v>
+        <v>13.6</v>
       </c>
       <c r="D56" t="n">
         <v>20</v>
@@ -1891,10 +1891,10 @@
         <v>0</v>
       </c>
       <c r="F56" t="n">
-        <v>1.232639789581299</v>
+        <v>1.25344705581665</v>
       </c>
       <c r="G56" t="n">
-        <v>195.7990362644196</v>
+        <v>201.4823005199432</v>
       </c>
       <c r="H56" t="n">
         <v>0</v>
@@ -1902,13 +1902,13 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>297.6989760398865</v>
+        <v>224.5429842472076</v>
       </c>
       <c r="B57" t="n">
-        <v>1425.8203125</v>
+        <v>1445.953125</v>
       </c>
       <c r="C57" t="n">
-        <v>13.4</v>
+        <v>13.8</v>
       </c>
       <c r="D57" t="n">
         <v>20</v>
@@ -1917,10 +1917,10 @@
         <v>0</v>
       </c>
       <c r="F57" t="n">
-        <v>1.279675245285034</v>
+        <v>1.222887277603149</v>
       </c>
       <c r="G57" t="n">
-        <v>296.4192986488342</v>
+        <v>223.3200941085815</v>
       </c>
       <c r="H57" t="n">
         <v>0</v>
@@ -1928,13 +1928,13 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>211.3234415054321</v>
+        <v>194.4991102218628</v>
       </c>
       <c r="B58" t="n">
-        <v>1425.8203125</v>
+        <v>1445.95703125</v>
       </c>
       <c r="C58" t="n">
-        <v>13.4</v>
+        <v>13.8</v>
       </c>
       <c r="D58" t="n">
         <v>20</v>
@@ -1943,10 +1943,10 @@
         <v>0</v>
       </c>
       <c r="F58" t="n">
-        <v>1.227201223373413</v>
+        <v>1.244938611984253</v>
       </c>
       <c r="G58" t="n">
-        <v>210.0962376594543</v>
+        <v>193.2541687488556</v>
       </c>
       <c r="H58" t="n">
         <v>0</v>
@@ -1954,13 +1954,13 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>173.9121851921082</v>
+        <v>193.0151836872101</v>
       </c>
       <c r="B59" t="n">
-        <v>1425.8203125</v>
+        <v>1445.9609375</v>
       </c>
       <c r="C59" t="n">
-        <v>13.1</v>
+        <v>13.6</v>
       </c>
       <c r="D59" t="n">
         <v>20</v>
@@ -1969,10 +1969,10 @@
         <v>0</v>
       </c>
       <c r="F59" t="n">
-        <v>1.502098083496094</v>
+        <v>1.442703723907471</v>
       </c>
       <c r="G59" t="n">
-        <v>172.4100849628448</v>
+        <v>191.5724775791168</v>
       </c>
       <c r="H59" t="n">
         <v>0</v>
@@ -1980,13 +1980,13 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>188.1288003921509</v>
+        <v>342.0660843849182</v>
       </c>
       <c r="B60" t="n">
-        <v>1425.8203125</v>
+        <v>1446.21484375</v>
       </c>
       <c r="C60" t="n">
-        <v>13.4</v>
+        <v>13.8</v>
       </c>
       <c r="D60" t="n">
         <v>20</v>
@@ -1995,10 +1995,10 @@
         <v>0</v>
       </c>
       <c r="F60" t="n">
-        <v>1.221950531005859</v>
+        <v>1.211202144622803</v>
       </c>
       <c r="G60" t="n">
-        <v>186.9068479537964</v>
+        <v>340.8548800945282</v>
       </c>
       <c r="H60" t="n">
         <v>0</v>
@@ -2006,13 +2006,13 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>185.7766962051392</v>
+        <v>196.8808014392853</v>
       </c>
       <c r="B61" t="n">
-        <v>1425.8203125</v>
+        <v>1446.21484375</v>
       </c>
       <c r="C61" t="n">
-        <v>13.3</v>
+        <v>13.7</v>
       </c>
       <c r="D61" t="n">
         <v>20</v>
@@ -2021,10 +2021,10 @@
         <v>0</v>
       </c>
       <c r="F61" t="n">
-        <v>1.277440547943115</v>
+        <v>1.255117177963257</v>
       </c>
       <c r="G61" t="n">
-        <v>184.4992532730103</v>
+        <v>195.6256816387177</v>
       </c>
       <c r="H61" t="n">
         <v>0</v>
@@ -2032,13 +2032,13 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>217.5486812591553</v>
+        <v>157.4113132953644</v>
       </c>
       <c r="B62" t="n">
-        <v>1425.8203125</v>
+        <v>1446.21484375</v>
       </c>
       <c r="C62" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="D62" t="n">
         <v>20</v>
@@ -2047,10 +2047,10 @@
         <v>0</v>
       </c>
       <c r="F62" t="n">
-        <v>1.420284271240234</v>
+        <v>1.350200176239014</v>
       </c>
       <c r="G62" t="n">
-        <v>216.1283946037292</v>
+        <v>156.061110496521</v>
       </c>
       <c r="H62" t="n">
         <v>0</v>
@@ -2058,13 +2058,13 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>145.0687770843506</v>
+        <v>177.8854670524597</v>
       </c>
       <c r="B63" t="n">
-        <v>1425.8203125</v>
+        <v>1446.21484375</v>
       </c>
       <c r="C63" t="n">
-        <v>13.2</v>
+        <v>13.8</v>
       </c>
       <c r="D63" t="n">
         <v>20</v>
@@ -2073,10 +2073,10 @@
         <v>0</v>
       </c>
       <c r="F63" t="n">
-        <v>1.456096887588501</v>
+        <v>1.214670181274414</v>
       </c>
       <c r="G63" t="n">
-        <v>143.6126778125763</v>
+        <v>176.6707942485809</v>
       </c>
       <c r="H63" t="n">
         <v>0</v>
@@ -2084,13 +2084,13 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>187.9322338104248</v>
+        <v>209.5704565048218</v>
       </c>
       <c r="B64" t="n">
-        <v>1425.8203125</v>
+        <v>1446.21484375</v>
       </c>
       <c r="C64" t="n">
-        <v>13.4</v>
+        <v>13.8</v>
       </c>
       <c r="D64" t="n">
         <v>20</v>
@@ -2099,10 +2099,10 @@
         <v>0</v>
       </c>
       <c r="F64" t="n">
-        <v>1.500192642211914</v>
+        <v>1.221551418304443</v>
       </c>
       <c r="G64" t="n">
-        <v>186.4320387840271</v>
+        <v>208.3489022254944</v>
       </c>
       <c r="H64" t="n">
         <v>0</v>
@@ -2110,13 +2110,13 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>168.4373672008514</v>
+        <v>155.6822469234467</v>
       </c>
       <c r="B65" t="n">
-        <v>1425.8203125</v>
+        <v>1446.21484375</v>
       </c>
       <c r="C65" t="n">
-        <v>13.3</v>
+        <v>13.5</v>
       </c>
       <c r="D65" t="n">
         <v>20</v>
@@ -2125,10 +2125,10 @@
         <v>0</v>
       </c>
       <c r="F65" t="n">
-        <v>1.283151865005493</v>
+        <v>1.248746871948242</v>
       </c>
       <c r="G65" t="n">
-        <v>167.1542131900787</v>
+        <v>154.4334971904755</v>
       </c>
       <c r="H65" t="n">
         <v>0</v>
@@ -2136,13 +2136,13 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>152.0732223987579</v>
+        <v>161.0369536876678</v>
       </c>
       <c r="B66" t="n">
-        <v>1425.8203125</v>
+        <v>1446.21484375</v>
       </c>
       <c r="C66" t="n">
-        <v>13.1</v>
+        <v>13.6</v>
       </c>
       <c r="D66" t="n">
         <v>20</v>
@@ -2151,10 +2151,10 @@
         <v>0</v>
       </c>
       <c r="F66" t="n">
-        <v>1.220553874969482</v>
+        <v>1.218591690063477</v>
       </c>
       <c r="G66" t="n">
-        <v>150.8526666164398</v>
+        <v>159.8183596134186</v>
       </c>
       <c r="H66" t="n">
         <v>0</v>
@@ -2162,13 +2162,13 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>1057.302765607834</v>
+        <v>178.8530859947205</v>
       </c>
       <c r="B67" t="n">
-        <v>1427.69921875</v>
+        <v>1446.21484375</v>
       </c>
       <c r="C67" t="n">
-        <v>11.6</v>
+        <v>13.5</v>
       </c>
       <c r="D67" t="n">
         <v>20</v>
@@ -2177,10 +2177,10 @@
         <v>0</v>
       </c>
       <c r="F67" t="n">
-        <v>1.523171663284302</v>
+        <v>1.55723237991333</v>
       </c>
       <c r="G67" t="n">
-        <v>1055.779591560364</v>
+        <v>177.2958514690399</v>
       </c>
       <c r="H67" t="n">
         <v>0</v>
@@ -2188,13 +2188,13 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>173.943398475647</v>
+        <v>209.3800349235535</v>
       </c>
       <c r="B68" t="n">
-        <v>1427.69921875</v>
+        <v>1446.21484375</v>
       </c>
       <c r="C68" t="n">
-        <v>13.4</v>
+        <v>13.8</v>
       </c>
       <c r="D68" t="n">
         <v>20</v>
@@ -2203,10 +2203,10 @@
         <v>0</v>
       </c>
       <c r="F68" t="n">
-        <v>1.281460285186768</v>
+        <v>1.227649927139282</v>
       </c>
       <c r="G68" t="n">
-        <v>172.661936044693</v>
+        <v>208.152382850647</v>
       </c>
       <c r="H68" t="n">
         <v>0</v>
